--- a/src/test/resources/DataDriven/LoginPage.xlsx
+++ b/src/test/resources/DataDriven/LoginPage.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2445" windowWidth="12540" windowHeight="4110"/>
+    <workbookView xWindow="0" yWindow="2445" windowWidth="12540" windowHeight="4110" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="186">
   <si>
     <t>Password</t>
   </si>
@@ -204,9 +205,6 @@
     <t>testuser@0g4tnuyv.mailosaur.net</t>
   </si>
   <si>
-    <t>testingteam508@gmail.com</t>
-  </si>
-  <si>
     <t>Empty Amount</t>
   </si>
   <si>
@@ -223,13 +221,367 @@
   </si>
   <si>
     <t>100.5</t>
+  </si>
+  <si>
+    <t>Fname</t>
+  </si>
+  <si>
+    <t>lanme</t>
+  </si>
+  <si>
+    <t>MobNo</t>
+  </si>
+  <si>
+    <t>AXIS</t>
+  </si>
+  <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>9807654345</t>
+  </si>
+  <si>
+    <t>567890</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>Paddr</t>
+  </si>
+  <si>
+    <t>Shop addr</t>
+  </si>
+  <si>
+    <t>Test franchisee</t>
+  </si>
+  <si>
+    <t>qwepl6543h</t>
+  </si>
+  <si>
+    <t>Mysuru</t>
+  </si>
+  <si>
+    <t>10-Jun-2000</t>
+  </si>
+  <si>
+    <t>560002</t>
+  </si>
+  <si>
+    <t>Pcode</t>
+  </si>
+  <si>
+    <t>New_Registration</t>
+  </si>
+  <si>
+    <t>MF_Reg</t>
+  </si>
+  <si>
+    <t>Aname</t>
+  </si>
+  <si>
+    <t>Mob</t>
+  </si>
+  <si>
+    <t>Test master</t>
+  </si>
+  <si>
+    <t>10-Oct-2000</t>
+  </si>
+  <si>
+    <t>9888888888</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>MF_OP</t>
+  </si>
+  <si>
+    <t>Fdate</t>
+  </si>
+  <si>
+    <t>01-OCT-2024</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>CMSSM</t>
+  </si>
+  <si>
+    <t>Test comment</t>
+  </si>
+  <si>
+    <t>Master Franchisee Registration Details-ReachMyIndia</t>
+  </si>
+  <si>
+    <t>Master Franchisee Registration Application Approved</t>
+  </si>
+  <si>
+    <t>master sub1</t>
+  </si>
+  <si>
+    <t>master sub2</t>
+  </si>
+  <si>
+    <t>D:\\Ramya\\Ramya Downloads\\190214.pdf</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Dob</t>
+  </si>
+  <si>
+    <t>10-Nov-2002</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Phone No</t>
+  </si>
+  <si>
+    <t>Mob No</t>
+  </si>
+  <si>
+    <t>Addr 1</t>
+  </si>
+  <si>
+    <t>Test TVS new</t>
+  </si>
+  <si>
+    <t>9908765435</t>
+  </si>
+  <si>
+    <t>8987654346</t>
+  </si>
+  <si>
+    <t>11-NOV-2006</t>
+  </si>
+  <si>
+    <t>123 Address</t>
+  </si>
+  <si>
+    <t>124 Address</t>
+  </si>
+  <si>
+    <t>567891</t>
+  </si>
+  <si>
+    <t>7654345678</t>
+  </si>
+  <si>
+    <t>11-NOV-2005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test TVS </t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Dist</t>
+  </si>
+  <si>
+    <t>Taluk</t>
+  </si>
+  <si>
+    <t>UTTAR PRADESH</t>
+  </si>
+  <si>
+    <t>HAPUR</t>
+  </si>
+  <si>
+    <t>DHAULANA</t>
+  </si>
+  <si>
+    <t>Prod</t>
+  </si>
+  <si>
+    <t>Track</t>
+  </si>
+  <si>
+    <t>Doctype</t>
+  </si>
+  <si>
+    <t>New Tractor Loan</t>
+  </si>
+  <si>
+    <t>Loan Statement Copy (LSC)</t>
+  </si>
+  <si>
+    <t>Track Based Personal Loan (AP)</t>
+  </si>
+  <si>
+    <t>Doc Name</t>
+  </si>
+  <si>
+    <t>Doc Path</t>
+  </si>
+  <si>
+    <t>Sname</t>
+  </si>
+  <si>
+    <t>agreement</t>
+  </si>
+  <si>
+    <t>D:\\Latest Docs and Downloads Backup\\Rentalagrement3.pdf</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>Ram</t>
+  </si>
+  <si>
+    <t>Sam</t>
+  </si>
+  <si>
+    <t>Cprice</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Article</t>
+  </si>
+  <si>
+    <t>Doc type</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ASDPL9876G</t>
+  </si>
+  <si>
+    <t>Pan Number</t>
+  </si>
+  <si>
+    <t>10-OCT-2000</t>
+  </si>
+  <si>
+    <t>Affidavit -4</t>
+  </si>
+  <si>
+    <t>testuser@h5elioah.mailosaur.net</t>
+  </si>
+  <si>
+    <t>testingteam171@gmail.com</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Forwarding to CMSSM</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>testing678@yahoo.co.in</t>
+  </si>
+  <si>
+    <t>Test approved</t>
+  </si>
+  <si>
+    <t>CACC</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Approved By SM</t>
+  </si>
+  <si>
+    <t>24-FEB-2025</t>
+  </si>
+  <si>
+    <t>Settlement Success</t>
+  </si>
+  <si>
+    <t>15-MAR-2025</t>
+  </si>
+  <si>
+    <t>Ref No</t>
+  </si>
+  <si>
+    <t>123123</t>
+  </si>
+  <si>
+    <t>settlement done</t>
+  </si>
+  <si>
+    <t>DDE Service Individual</t>
+  </si>
+  <si>
+    <t>DDE Entity</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Pan</t>
+  </si>
+  <si>
+    <t>Legal</t>
+  </si>
+  <si>
+    <t>Dateofincorp</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>comm add</t>
+  </si>
+  <si>
+    <t>comm pin</t>
+  </si>
+  <si>
+    <t>9876543211</t>
+  </si>
+  <si>
+    <t>10-10-2024</t>
+  </si>
+  <si>
+    <t>560098</t>
+  </si>
+  <si>
+    <t>456098</t>
+  </si>
+  <si>
+    <t>MLNCR5432K</t>
+  </si>
+  <si>
+    <t>Proprietorship</t>
+  </si>
+  <si>
+    <t>test_mail_123@outlook.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,6 +611,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -301,7 +668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -312,22 +679,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -338,6 +713,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -386,7 +764,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -421,7 +799,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -630,22 +1008,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" customWidth="1"/>
     <col min="4" max="4" width="20.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="36.28515625" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
     <col min="8" max="8" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>36</v>
       </c>
@@ -655,7 +1033,7 @@
       <c r="D1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G1" s="6" t="s">
@@ -665,25 +1043,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D2" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D2" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -692,24 +1070,37 @@
       <c r="E4" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="23"/>
+      <c r="F5" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5"/>
@@ -719,30 +1110,30 @@
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>54</v>
       </c>
@@ -765,40 +1156,62 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -810,44 +1223,76 @@
       <c r="E13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="E15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>61</v>
+      <c r="C16" s="28" t="s">
+        <v>151</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
+      <c r="E16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -857,28 +1302,36 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="2"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="20" t="s">
         <v>49</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="17" t="s">
         <v>51</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="6" t="s">
@@ -887,38 +1340,62 @@
       <c r="D20" s="6" t="s">
         <v>52</v>
       </c>
+      <c r="F20" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="C22" s="17" t="s">
         <v>64</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="2"/>
+      <c r="F24" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2"/>
+      <c r="C25" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
@@ -927,6 +1404,12 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
+      <c r="F27" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -934,6 +1417,12 @@
       </c>
       <c r="B28" t="s">
         <v>2</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -972,43 +1461,45 @@
   <hyperlinks>
     <hyperlink ref="E1" r:id="rId1"/>
     <hyperlink ref="C16" r:id="rId2"/>
-    <hyperlink ref="B5" r:id="rId3"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="G5" r:id="rId4"/>
+    <hyperlink ref="G17" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId4"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" customWidth="1"/>
-    <col min="4" max="4" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="48.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="17" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -1019,13 +1510,34 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="7" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1034,17 +1546,489 @@
     <hyperlink ref="A5" r:id="rId2"/>
     <hyperlink ref="A6" r:id="rId3"/>
     <hyperlink ref="A2" r:id="rId4"/>
+    <hyperlink ref="A7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="32.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="17"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="6"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C21" r:id="rId1"/>
+    <hyperlink ref="E7" r:id="rId2"/>
+    <hyperlink ref="F16" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="5" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="40.140625" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M1" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B14" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="157" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>